--- a/InputData/fuels/FPIEBP/Fuel Prod Imp Exp Balancing Priorities.xlsx
+++ b/InputData/fuels/FPIEBP/Fuel Prod Imp Exp Balancing Priorities.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olivia\Documents\EPS_Models by Region\RMI\RMI_all_states\NE\fuels\FPIEBP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\fuels\FPIEBP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B198527-1971-4F56-9966-3B4BA9579031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4E0A33-3857-4E42-99DE-F3DBB58130FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="12735" activeTab="1" xr2:uid="{B505BEC9-7B7D-48ED-A025-9B3B4252ED08}"/>
+    <workbookView xWindow="18705" yWindow="1695" windowWidth="19470" windowHeight="20340" xr2:uid="{B505BEC9-7B7D-48ED-A025-9B3B4252ED08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
   <si>
     <t>FPIEBP Fuel Production Import Export Balancing Priorities</t>
   </si>
@@ -224,9 +224,6 @@
   </si>
   <si>
     <t>exports</t>
-  </si>
-  <si>
-    <t>Nebraska</t>
   </si>
 </sst>
 </file>
@@ -290,17 +287,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -616,20 +615,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290315BF-FDD8-4070-97AB-AF459B926789}">
   <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="7">
-        <v>44872</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -637,50 +630,50 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -721,12 +714,12 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -754,7 +747,7 @@
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="A37" s="2" t="s">
         <v>22</v>
       </c>
     </row>
@@ -834,15 +827,15 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.28515625" customWidth="1"/>
     <col min="2" max="4" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>59</v>
       </c>
       <c r="B1" t="s">
@@ -855,22 +848,22 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="5">
-        <v>0</v>
-      </c>
-      <c r="C2" s="5">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B2" s="7">
+        <v>0</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0</v>
+      </c>
+      <c r="D2" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B3">
@@ -883,22 +876,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B5">
@@ -911,235 +904,236 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="5">
-        <v>0</v>
-      </c>
-      <c r="C6" s="5">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="B6" s="7">
+        <v>0</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0</v>
+      </c>
+      <c r="D6" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="5">
-        <v>0</v>
-      </c>
-      <c r="C7" s="5">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="B7" s="7">
+        <v>0</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="5">
-        <v>0</v>
-      </c>
-      <c r="C8" s="5">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B8" s="7">
+        <v>0</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B9" s="9">
+        <v>1</v>
+      </c>
+      <c r="C9" s="9">
+        <v>3</v>
+      </c>
+      <c r="D9" s="9">
+        <v>2</v>
+      </c>
+      <c r="E9" s="9"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B10" s="9">
+        <v>1</v>
+      </c>
+      <c r="C10" s="9">
+        <v>3</v>
+      </c>
+      <c r="D10" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B11" s="9">
+        <v>1</v>
+      </c>
+      <c r="C11" s="9">
+        <v>3</v>
+      </c>
+      <c r="D11" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B12" s="9">
+        <v>1</v>
+      </c>
+      <c r="C12" s="9">
+        <v>3</v>
+      </c>
+      <c r="D12" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B13" s="9">
+        <v>1</v>
+      </c>
+      <c r="C13" s="9">
+        <v>2</v>
+      </c>
+      <c r="D13" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>3</v>
-      </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="B14" s="9">
+        <v>1</v>
+      </c>
+      <c r="C14" s="9">
+        <v>3</v>
+      </c>
+      <c r="D14" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="5">
-        <v>0</v>
-      </c>
-      <c r="C15" s="5">
-        <v>0</v>
-      </c>
-      <c r="D15" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="B15" s="7">
+        <v>0</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0</v>
+      </c>
+      <c r="D15" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="5">
-        <v>0</v>
-      </c>
-      <c r="C16" s="5">
-        <v>0</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="B16" s="7">
+        <v>0</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0</v>
+      </c>
+      <c r="D16" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17">
-        <v>3</v>
-      </c>
-      <c r="D17">
+      <c r="B17" s="9">
+        <v>1</v>
+      </c>
+      <c r="C17" s="9">
+        <v>3</v>
+      </c>
+      <c r="D17" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B18">
-        <v>2</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
+      <c r="B18" s="9">
+        <v>2</v>
+      </c>
+      <c r="C18" s="9">
+        <v>1</v>
+      </c>
+      <c r="D18" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>3</v>
-      </c>
-      <c r="D19">
+      <c r="B19" s="9">
+        <v>1</v>
+      </c>
+      <c r="C19" s="9">
+        <v>3</v>
+      </c>
+      <c r="D19" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20">
-        <v>3</v>
-      </c>
-      <c r="D20">
+      <c r="B20" s="9">
+        <v>1</v>
+      </c>
+      <c r="C20" s="9">
+        <v>3</v>
+      </c>
+      <c r="D20" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>3</v>
-      </c>
-      <c r="D21">
+      <c r="B21" s="9">
+        <v>1</v>
+      </c>
+      <c r="C21" s="9">
+        <v>3</v>
+      </c>
+      <c r="D21" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="9">
         <v>1</v>
       </c>
       <c r="C22">

--- a/InputData/fuels/FPIEBP/Fuel Prod Imp Exp Balancing Priorities.xlsx
+++ b/InputData/fuels/FPIEBP/Fuel Prod Imp Exp Balancing Priorities.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\fuels\FPIEBP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\NE\fuels\FPIEBP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4E0A33-3857-4E42-99DE-F3DBB58130FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC196ED5-B194-43BB-9925-9FEC127658E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18705" yWindow="1695" windowWidth="19470" windowHeight="20340" xr2:uid="{B505BEC9-7B7D-48ED-A025-9B3B4252ED08}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{B505BEC9-7B7D-48ED-A025-9B3B4252ED08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
   <si>
     <t>FPIEBP Fuel Production Import Export Balancing Priorities</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>exports</t>
+  </si>
+  <si>
+    <t>Nebraska</t>
   </si>
 </sst>
 </file>
@@ -287,19 +290,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -617,12 +618,18 @@
   <dimension ref="A1:D53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="7">
+        <v>45294</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -630,50 +637,50 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -714,12 +721,12 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -747,7 +754,7 @@
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+      <c r="A37" t="s">
         <v>22</v>
       </c>
     </row>
@@ -827,15 +834,15 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.28515625" customWidth="1"/>
     <col min="2" max="4" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>59</v>
       </c>
       <c r="B1" t="s">
@@ -848,292 +855,291 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="7">
-        <v>0</v>
-      </c>
-      <c r="C2" s="7">
-        <v>0</v>
-      </c>
-      <c r="D2" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B2" s="5">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>39</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>40</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>41</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="7">
-        <v>0</v>
-      </c>
-      <c r="C6" s="7">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="B6" s="5">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="7">
-        <v>0</v>
-      </c>
-      <c r="C7" s="7">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="B7" s="5">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="7">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="B8" s="5">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="9">
-        <v>1</v>
-      </c>
-      <c r="C9" s="9">
-        <v>3</v>
-      </c>
-      <c r="D9" s="9">
-        <v>2</v>
-      </c>
-      <c r="E9" s="9"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="9">
-        <v>1</v>
-      </c>
-      <c r="C10" s="9">
-        <v>3</v>
-      </c>
-      <c r="D10" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="9">
-        <v>1</v>
-      </c>
-      <c r="C11" s="9">
-        <v>3</v>
-      </c>
-      <c r="D11" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="9">
-        <v>1</v>
-      </c>
-      <c r="C12" s="9">
-        <v>3</v>
-      </c>
-      <c r="D12" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="9">
-        <v>1</v>
-      </c>
-      <c r="C13" s="9">
-        <v>2</v>
-      </c>
-      <c r="D13" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="9">
-        <v>1</v>
-      </c>
-      <c r="C14" s="9">
-        <v>3</v>
-      </c>
-      <c r="D14" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="7">
-        <v>0</v>
-      </c>
-      <c r="C15" s="7">
-        <v>0</v>
-      </c>
-      <c r="D15" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="B15" s="5">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="7">
-        <v>0</v>
-      </c>
-      <c r="C16" s="7">
-        <v>0</v>
-      </c>
-      <c r="D16" s="7">
+      <c r="B16" s="5">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="9">
-        <v>1</v>
-      </c>
-      <c r="C17" s="9">
-        <v>3</v>
-      </c>
-      <c r="D17" s="9">
-        <v>2</v>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="A18" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="9">
-        <v>2</v>
-      </c>
-      <c r="C18" s="9">
-        <v>1</v>
-      </c>
-      <c r="D18" s="9">
-        <v>3</v>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="A19" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="9">
-        <v>1</v>
-      </c>
-      <c r="C19" s="9">
-        <v>3</v>
-      </c>
-      <c r="D19" s="9">
-        <v>2</v>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="9">
-        <v>1</v>
-      </c>
-      <c r="C20" s="9">
-        <v>3</v>
-      </c>
-      <c r="D20" s="9">
-        <v>2</v>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="A21" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="9">
-        <v>1</v>
-      </c>
-      <c r="C21" s="9">
-        <v>3</v>
-      </c>
-      <c r="D21" s="9">
-        <v>2</v>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22">
         <v>1</v>
       </c>
       <c r="C22">

--- a/InputData/fuels/FPIEBP/Fuel Prod Imp Exp Balancing Priorities.xlsx
+++ b/InputData/fuels/FPIEBP/Fuel Prod Imp Exp Balancing Priorities.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\NE\fuels\FPIEBP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\NE\fuels\FPIEBP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9554F25E-88DA-4CA2-92E6-2C0770E0C9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1E4164A-DDE3-4335-AFE7-DB57937964AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="130" yWindow="130" windowWidth="14030" windowHeight="10155" activeTab="3" xr2:uid="{B505BEC9-7B7D-48ED-A025-9B3B4252ED08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{B505BEC9-7B7D-48ED-A025-9B3B4252ED08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -969,7 +969,7 @@
         <v>146</v>
       </c>
       <c r="C1" s="7">
-        <v>45391</v>
+        <v>46185</v>
       </c>
       <c r="F1" s="9" t="s">
         <v>122</v>
